--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF98D378-E54E-4CE0-97F8-6434A4C98C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88C15B4A-E029-4363-851D-B59C0ED84FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5441,7 +5441,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1969FC93-564F-400B-9296-322EAA3B637A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC27DBB9-71BD-4FC0-A1C8-74CEC9F698D4}">
   <dimension ref="B9:D248"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8085,7 +8085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F6B4BF-D58F-4707-A11C-D47627FC370F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989AF825-AC80-4291-85AC-2D58401542FE}">
   <dimension ref="B2:D241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BFCE000-0303-44FE-87B3-D810783A4595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B62D63-C964-45E3-8BC0-EA297242A488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6725,7 +6725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED6EA9C-3E4C-4261-AC3F-0EAB516749D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68F0C6A-3DDE-4C92-BBC2-852BC788A30A}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14077,7 +14077,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD4E5D4-00B2-48E6-AD1B-69B8B98A90BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EFACAD-9B55-44F5-9B7F-AF5F2C4A0216}">
   <dimension ref="B2:D669"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16ACD287-CA5A-4432-9D50-F965B956065B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCE6C87-D8C9-4D93-8ADF-A0AD29051DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4929" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="986">
   <si>
     <t>Unit</t>
   </si>
@@ -3015,6 +3015,9 @@
   </si>
   <si>
     <t>Nelson City</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>Taranaki</t>
@@ -9126,24 +9129,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84B9DDA-8008-48B0-AF7A-DABF3040022A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8191D3E7-570D-4EF7-8FD1-42D7F5B3DFC2}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C10" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -16478,7 +16481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A63592-906C-4559-AEBC-8F1C28942012}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EDAB4F-EA3A-461C-A84D-991CDA6B1EB1}">
   <dimension ref="B9:H676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17566,6 +17569,9 @@
       <c r="G63" t="s">
         <v>964</v>
       </c>
+      <c r="H63" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
@@ -17923,6 +17929,9 @@
       <c r="G81" t="s">
         <v>964</v>
       </c>
+      <c r="H81" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="82" spans="2:8">
       <c r="B82" t="s">
@@ -18161,7 +18170,7 @@
         <v>964</v>
       </c>
       <c r="H93" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -19100,6 +19109,9 @@
       <c r="G140" t="s">
         <v>964</v>
       </c>
+      <c r="H140" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="141" spans="2:8">
       <c r="B141" t="s">
@@ -19298,7 +19310,7 @@
         <v>964</v>
       </c>
       <c r="H150" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="151" spans="2:8">
@@ -19438,7 +19450,7 @@
         <v>964</v>
       </c>
       <c r="H157" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="158" spans="2:8">
@@ -19578,7 +19590,7 @@
         <v>964</v>
       </c>
       <c r="H164" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="165" spans="2:8">
@@ -19717,6 +19729,9 @@
       <c r="G171" t="s">
         <v>964</v>
       </c>
+      <c r="H171" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="172" spans="2:8">
       <c r="B172" t="s">
@@ -19734,6 +19749,9 @@
       <c r="G172" t="s">
         <v>964</v>
       </c>
+      <c r="H172" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="173" spans="2:8">
       <c r="B173" t="s">
@@ -19792,7 +19810,7 @@
         <v>964</v>
       </c>
       <c r="H175" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="176" spans="2:8">
@@ -19812,7 +19830,7 @@
         <v>964</v>
       </c>
       <c r="H176" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="177" spans="2:8">
@@ -19832,7 +19850,7 @@
         <v>964</v>
       </c>
       <c r="H177" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="178" spans="2:8">
@@ -19912,7 +19930,7 @@
         <v>964</v>
       </c>
       <c r="H181" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="182" spans="2:8">
@@ -19952,7 +19970,7 @@
         <v>964</v>
       </c>
       <c r="H183" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -19972,7 +19990,7 @@
         <v>964</v>
       </c>
       <c r="H184" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="185" spans="2:8">
@@ -19991,6 +20009,9 @@
       <c r="G185" t="s">
         <v>964</v>
       </c>
+      <c r="H185" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="186" spans="2:8">
       <c r="B186" t="s">
@@ -20069,7 +20090,7 @@
         <v>964</v>
       </c>
       <c r="H189" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="190" spans="2:8">
@@ -20128,6 +20149,9 @@
       <c r="G192" t="s">
         <v>964</v>
       </c>
+      <c r="H192" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="193" spans="2:8">
       <c r="B193" t="s">
@@ -20145,6 +20169,9 @@
       <c r="G193" t="s">
         <v>964</v>
       </c>
+      <c r="H193" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="194" spans="2:8">
       <c r="B194" t="s">
@@ -20162,6 +20189,9 @@
       <c r="G194" t="s">
         <v>964</v>
       </c>
+      <c r="H194" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="195" spans="2:8">
       <c r="B195" t="s">
@@ -20179,6 +20209,9 @@
       <c r="G195" t="s">
         <v>964</v>
       </c>
+      <c r="H195" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="196" spans="2:8">
       <c r="B196" t="s">
@@ -20217,7 +20250,7 @@
         <v>964</v>
       </c>
       <c r="H197" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="198" spans="2:8">
@@ -20237,7 +20270,7 @@
         <v>964</v>
       </c>
       <c r="H198" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="199" spans="2:8">
@@ -20256,6 +20289,9 @@
       <c r="G199" t="s">
         <v>964</v>
       </c>
+      <c r="H199" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="200" spans="2:8">
       <c r="B200" t="s">
@@ -20313,6 +20349,9 @@
       <c r="G202" t="s">
         <v>964</v>
       </c>
+      <c r="H202" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="203" spans="2:8">
       <c r="B203" t="s">
@@ -20330,6 +20369,9 @@
       <c r="G203" t="s">
         <v>964</v>
       </c>
+      <c r="H203" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="204" spans="2:8">
       <c r="B204" t="s">
@@ -20347,6 +20389,9 @@
       <c r="G204" t="s">
         <v>964</v>
       </c>
+      <c r="H204" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="205" spans="2:8">
       <c r="B205" t="s">
@@ -20365,7 +20410,7 @@
         <v>964</v>
       </c>
       <c r="H205" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="206" spans="2:8">
@@ -20384,6 +20429,9 @@
       <c r="G206" t="s">
         <v>964</v>
       </c>
+      <c r="H206" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="207" spans="2:8">
       <c r="B207" t="s">
@@ -20401,6 +20449,9 @@
       <c r="G207" t="s">
         <v>964</v>
       </c>
+      <c r="H207" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="208" spans="2:8">
       <c r="B208" t="s">
@@ -20478,6 +20529,9 @@
       <c r="G211" t="s">
         <v>964</v>
       </c>
+      <c r="H211" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="212" spans="2:8">
       <c r="B212" t="s">
@@ -20495,6 +20549,9 @@
       <c r="G212" t="s">
         <v>964</v>
       </c>
+      <c r="H212" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="213" spans="2:8">
       <c r="B213" t="s">
@@ -20552,6 +20609,9 @@
       <c r="G215" t="s">
         <v>964</v>
       </c>
+      <c r="H215" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="216" spans="2:8">
       <c r="B216" t="s">
@@ -20709,6 +20769,9 @@
       <c r="G223" t="s">
         <v>964</v>
       </c>
+      <c r="H223" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="224" spans="2:8">
       <c r="B224" t="s">
@@ -20726,6 +20789,9 @@
       <c r="G224" t="s">
         <v>964</v>
       </c>
+      <c r="H224" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="225" spans="2:8">
       <c r="B225" t="s">
@@ -20943,6 +21009,9 @@
       <c r="G235" t="s">
         <v>964</v>
       </c>
+      <c r="H235" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="236" spans="2:8">
       <c r="B236" t="s">
@@ -21101,7 +21170,7 @@
         <v>964</v>
       </c>
       <c r="H243" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="244" spans="2:8">
@@ -21141,7 +21210,7 @@
         <v>964</v>
       </c>
       <c r="H245" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="246" spans="2:8">
@@ -21161,7 +21230,7 @@
         <v>964</v>
       </c>
       <c r="H246" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="247" spans="2:8">
@@ -21180,6 +21249,9 @@
       <c r="G247" t="s">
         <v>964</v>
       </c>
+      <c r="H247" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="248" spans="2:8">
       <c r="B248" t="s">
@@ -21197,6 +21269,9 @@
       <c r="G248" t="s">
         <v>964</v>
       </c>
+      <c r="H248" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="249" spans="2:8">
       <c r="B249" t="s">
@@ -21214,6 +21289,9 @@
       <c r="G249" t="s">
         <v>964</v>
       </c>
+      <c r="H249" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="250" spans="2:8">
       <c r="B250" t="s">
@@ -21231,6 +21309,9 @@
       <c r="G250" t="s">
         <v>964</v>
       </c>
+      <c r="H250" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="251" spans="2:8">
       <c r="B251" t="s">
@@ -21248,6 +21329,9 @@
       <c r="G251" t="s">
         <v>964</v>
       </c>
+      <c r="H251" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="252" spans="2:8">
       <c r="B252" t="s">
@@ -21265,6 +21349,9 @@
       <c r="G252" t="s">
         <v>964</v>
       </c>
+      <c r="H252" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="253" spans="2:8">
       <c r="B253" t="s">
@@ -21282,6 +21369,9 @@
       <c r="G253" t="s">
         <v>964</v>
       </c>
+      <c r="H253" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="254" spans="2:8">
       <c r="B254" t="s">
@@ -21299,6 +21389,9 @@
       <c r="G254" t="s">
         <v>964</v>
       </c>
+      <c r="H254" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="255" spans="2:8">
       <c r="B255" t="s">
@@ -21316,6 +21409,9 @@
       <c r="G255" t="s">
         <v>964</v>
       </c>
+      <c r="H255" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="256" spans="2:8">
       <c r="B256" t="s">
@@ -21333,8 +21429,11 @@
       <c r="G256" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="257" spans="2:7">
+      <c r="H256" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="257" spans="2:8">
       <c r="B257" t="s">
         <v>297</v>
       </c>
@@ -21350,8 +21449,11 @@
       <c r="G257" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="258" spans="2:7">
+      <c r="H257" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="258" spans="2:8">
       <c r="B258" t="s">
         <v>297</v>
       </c>
@@ -21367,8 +21469,11 @@
       <c r="G258" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="259" spans="2:7">
+      <c r="H258" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="259" spans="2:8">
       <c r="B259" t="s">
         <v>297</v>
       </c>
@@ -21384,8 +21489,11 @@
       <c r="G259" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="260" spans="2:7">
+      <c r="H259" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="260" spans="2:8">
       <c r="B260" t="s">
         <v>297</v>
       </c>
@@ -21401,8 +21509,11 @@
       <c r="G260" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="261" spans="2:7">
+      <c r="H260" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="261" spans="2:8">
       <c r="B261" t="s">
         <v>297</v>
       </c>
@@ -21418,8 +21529,11 @@
       <c r="G261" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="262" spans="2:7">
+      <c r="H261" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="262" spans="2:8">
       <c r="B262" t="s">
         <v>297</v>
       </c>
@@ -21435,8 +21549,11 @@
       <c r="G262" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="263" spans="2:7">
+      <c r="H262" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="263" spans="2:8">
       <c r="B263" t="s">
         <v>297</v>
       </c>
@@ -21452,8 +21569,11 @@
       <c r="G263" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="264" spans="2:7">
+      <c r="H263" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="264" spans="2:8">
       <c r="B264" t="s">
         <v>297</v>
       </c>
@@ -21469,8 +21589,11 @@
       <c r="G264" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="265" spans="2:7">
+      <c r="H264" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="265" spans="2:8">
       <c r="B265" t="s">
         <v>297</v>
       </c>
@@ -21486,8 +21609,11 @@
       <c r="G265" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="266" spans="2:7">
+      <c r="H265" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="266" spans="2:8">
       <c r="B266" t="s">
         <v>297</v>
       </c>
@@ -21503,8 +21629,11 @@
       <c r="G266" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="267" spans="2:7">
+      <c r="H266" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="267" spans="2:8">
       <c r="B267" t="s">
         <v>297</v>
       </c>
@@ -21520,8 +21649,11 @@
       <c r="G267" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="268" spans="2:7">
+      <c r="H267" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="268" spans="2:8">
       <c r="B268" t="s">
         <v>297</v>
       </c>
@@ -21537,8 +21669,11 @@
       <c r="G268" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="269" spans="2:7">
+      <c r="H268" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="269" spans="2:8">
       <c r="B269" t="s">
         <v>297</v>
       </c>
@@ -21554,8 +21689,11 @@
       <c r="G269" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="270" spans="2:7">
+      <c r="H269" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="270" spans="2:8">
       <c r="B270" t="s">
         <v>297</v>
       </c>
@@ -21571,8 +21709,11 @@
       <c r="G270" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="271" spans="2:7">
+      <c r="H270" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="271" spans="2:8">
       <c r="B271" t="s">
         <v>297</v>
       </c>
@@ -21588,8 +21729,11 @@
       <c r="G271" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="272" spans="2:7">
+      <c r="H271" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="272" spans="2:8">
       <c r="B272" t="s">
         <v>297</v>
       </c>
@@ -21605,8 +21749,11 @@
       <c r="G272" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="273" spans="2:7">
+      <c r="H272" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="273" spans="2:8">
       <c r="B273" t="s">
         <v>297</v>
       </c>
@@ -21622,8 +21769,11 @@
       <c r="G273" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="274" spans="2:7">
+      <c r="H273" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="274" spans="2:8">
       <c r="B274" t="s">
         <v>297</v>
       </c>
@@ -21639,8 +21789,11 @@
       <c r="G274" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="275" spans="2:7">
+      <c r="H274" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="275" spans="2:8">
       <c r="B275" t="s">
         <v>297</v>
       </c>
@@ -21656,8 +21809,11 @@
       <c r="G275" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="276" spans="2:7">
+      <c r="H275" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="276" spans="2:8">
       <c r="B276" t="s">
         <v>297</v>
       </c>
@@ -21673,8 +21829,11 @@
       <c r="G276" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="277" spans="2:7">
+      <c r="H276" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="277" spans="2:8">
       <c r="B277" t="s">
         <v>297</v>
       </c>
@@ -21690,8 +21849,11 @@
       <c r="G277" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="278" spans="2:7">
+      <c r="H277" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="278" spans="2:8">
       <c r="B278" t="s">
         <v>297</v>
       </c>
@@ -21707,8 +21869,11 @@
       <c r="G278" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="279" spans="2:7">
+      <c r="H278" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="279" spans="2:8">
       <c r="B279" t="s">
         <v>297</v>
       </c>
@@ -21724,8 +21889,11 @@
       <c r="G279" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="280" spans="2:7">
+      <c r="H279" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="280" spans="2:8">
       <c r="B280" t="s">
         <v>297</v>
       </c>
@@ -21741,8 +21909,11 @@
       <c r="G280" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="281" spans="2:7">
+      <c r="H280" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="281" spans="2:8">
       <c r="B281" t="s">
         <v>297</v>
       </c>
@@ -21758,8 +21929,11 @@
       <c r="G281" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="282" spans="2:7">
+      <c r="H281" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="282" spans="2:8">
       <c r="B282" t="s">
         <v>297</v>
       </c>
@@ -21775,8 +21949,11 @@
       <c r="G282" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="283" spans="2:7">
+      <c r="H282" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="283" spans="2:8">
       <c r="B283" t="s">
         <v>297</v>
       </c>
@@ -21792,8 +21969,11 @@
       <c r="G283" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="284" spans="2:7">
+      <c r="H283" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="284" spans="2:8">
       <c r="B284" t="s">
         <v>297</v>
       </c>
@@ -21809,8 +21989,11 @@
       <c r="G284" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="285" spans="2:7">
+      <c r="H284" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="285" spans="2:8">
       <c r="B285" t="s">
         <v>297</v>
       </c>
@@ -21826,8 +22009,11 @@
       <c r="G285" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="286" spans="2:7">
+      <c r="H285" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="286" spans="2:8">
       <c r="B286" t="s">
         <v>297</v>
       </c>
@@ -21843,8 +22029,11 @@
       <c r="G286" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="287" spans="2:7">
+      <c r="H286" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="287" spans="2:8">
       <c r="B287" t="s">
         <v>297</v>
       </c>
@@ -21860,8 +22049,11 @@
       <c r="G287" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="288" spans="2:7">
+      <c r="H287" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="288" spans="2:8">
       <c r="B288" t="s">
         <v>297</v>
       </c>
@@ -21877,6 +22069,9 @@
       <c r="G288" t="s">
         <v>964</v>
       </c>
+      <c r="H288" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="289" spans="2:8">
       <c r="B289" t="s">
@@ -21894,6 +22089,9 @@
       <c r="G289" t="s">
         <v>964</v>
       </c>
+      <c r="H289" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="290" spans="2:8">
       <c r="B290" t="s">
@@ -21911,6 +22109,9 @@
       <c r="G290" t="s">
         <v>964</v>
       </c>
+      <c r="H290" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="291" spans="2:8">
       <c r="B291" t="s">
@@ -21928,6 +22129,9 @@
       <c r="G291" t="s">
         <v>964</v>
       </c>
+      <c r="H291" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="292" spans="2:8">
       <c r="B292" t="s">
@@ -21945,6 +22149,9 @@
       <c r="G292" t="s">
         <v>964</v>
       </c>
+      <c r="H292" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="293" spans="2:8">
       <c r="B293" t="s">
@@ -21962,6 +22169,9 @@
       <c r="G293" t="s">
         <v>964</v>
       </c>
+      <c r="H293" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="294" spans="2:8">
       <c r="B294" t="s">
@@ -21979,6 +22189,9 @@
       <c r="G294" t="s">
         <v>964</v>
       </c>
+      <c r="H294" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="295" spans="2:8">
       <c r="B295" t="s">
@@ -21996,6 +22209,9 @@
       <c r="G295" t="s">
         <v>964</v>
       </c>
+      <c r="H295" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="296" spans="2:8">
       <c r="B296" t="s">
@@ -22033,6 +22249,9 @@
       <c r="G297" t="s">
         <v>964</v>
       </c>
+      <c r="H297" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="298" spans="2:8">
       <c r="B298" t="s">
@@ -22050,6 +22269,9 @@
       <c r="G298" t="s">
         <v>964</v>
       </c>
+      <c r="H298" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="299" spans="2:8">
       <c r="B299" t="s">
@@ -22067,6 +22289,9 @@
       <c r="G299" t="s">
         <v>964</v>
       </c>
+      <c r="H299" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="300" spans="2:8">
       <c r="B300" t="s">
@@ -22084,6 +22309,9 @@
       <c r="G300" t="s">
         <v>964</v>
       </c>
+      <c r="H300" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="301" spans="2:8">
       <c r="B301" t="s">
@@ -22101,6 +22329,9 @@
       <c r="G301" t="s">
         <v>964</v>
       </c>
+      <c r="H301" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="302" spans="2:8">
       <c r="B302" t="s">
@@ -22118,6 +22349,9 @@
       <c r="G302" t="s">
         <v>964</v>
       </c>
+      <c r="H302" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="303" spans="2:8">
       <c r="B303" t="s">
@@ -22135,6 +22369,9 @@
       <c r="G303" t="s">
         <v>964</v>
       </c>
+      <c r="H303" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="304" spans="2:8">
       <c r="B304" t="s">
@@ -22152,6 +22389,9 @@
       <c r="G304" t="s">
         <v>964</v>
       </c>
+      <c r="H304" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="305" spans="2:8">
       <c r="B305" t="s">
@@ -22169,6 +22409,9 @@
       <c r="G305" t="s">
         <v>964</v>
       </c>
+      <c r="H305" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="306" spans="2:8">
       <c r="B306" t="s">
@@ -22186,6 +22429,9 @@
       <c r="G306" t="s">
         <v>964</v>
       </c>
+      <c r="H306" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="307" spans="2:8">
       <c r="B307" t="s">
@@ -22203,6 +22449,9 @@
       <c r="G307" t="s">
         <v>964</v>
       </c>
+      <c r="H307" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="308" spans="2:8">
       <c r="B308" t="s">
@@ -22220,6 +22469,9 @@
       <c r="G308" t="s">
         <v>964</v>
       </c>
+      <c r="H308" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="309" spans="2:8">
       <c r="B309" t="s">
@@ -22237,6 +22489,9 @@
       <c r="G309" t="s">
         <v>964</v>
       </c>
+      <c r="H309" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="310" spans="2:8">
       <c r="B310" t="s">
@@ -22254,6 +22509,9 @@
       <c r="G310" t="s">
         <v>964</v>
       </c>
+      <c r="H310" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="311" spans="2:8">
       <c r="B311" t="s">
@@ -22271,6 +22529,9 @@
       <c r="G311" t="s">
         <v>964</v>
       </c>
+      <c r="H311" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="312" spans="2:8">
       <c r="B312" t="s">
@@ -22288,6 +22549,9 @@
       <c r="G312" t="s">
         <v>964</v>
       </c>
+      <c r="H312" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="313" spans="2:8">
       <c r="B313" t="s">
@@ -22345,6 +22609,9 @@
       <c r="G315" t="s">
         <v>964</v>
       </c>
+      <c r="H315" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="316" spans="2:8">
       <c r="B316" t="s">
@@ -22362,6 +22629,9 @@
       <c r="G316" t="s">
         <v>964</v>
       </c>
+      <c r="H316" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="317" spans="2:8">
       <c r="B317" t="s">
@@ -22379,6 +22649,9 @@
       <c r="G317" t="s">
         <v>964</v>
       </c>
+      <c r="H317" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="318" spans="2:8">
       <c r="B318" t="s">
@@ -22396,6 +22669,9 @@
       <c r="G318" t="s">
         <v>964</v>
       </c>
+      <c r="H318" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="319" spans="2:8">
       <c r="B319" t="s">
@@ -22413,6 +22689,9 @@
       <c r="G319" t="s">
         <v>964</v>
       </c>
+      <c r="H319" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="320" spans="2:8">
       <c r="B320" t="s">
@@ -22430,6 +22709,9 @@
       <c r="G320" t="s">
         <v>964</v>
       </c>
+      <c r="H320" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="321" spans="2:8">
       <c r="B321" t="s">
@@ -22447,6 +22729,9 @@
       <c r="G321" t="s">
         <v>964</v>
       </c>
+      <c r="H321" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="322" spans="2:8">
       <c r="B322" t="s">
@@ -22464,6 +22749,9 @@
       <c r="G322" t="s">
         <v>964</v>
       </c>
+      <c r="H322" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="323" spans="2:8">
       <c r="B323" t="s">
@@ -22481,6 +22769,9 @@
       <c r="G323" t="s">
         <v>964</v>
       </c>
+      <c r="H323" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="324" spans="2:8">
       <c r="B324" t="s">
@@ -22498,6 +22789,9 @@
       <c r="G324" t="s">
         <v>964</v>
       </c>
+      <c r="H324" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="325" spans="2:8">
       <c r="B325" t="s">
@@ -22515,6 +22809,9 @@
       <c r="G325" t="s">
         <v>964</v>
       </c>
+      <c r="H325" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="326" spans="2:8">
       <c r="B326" t="s">
@@ -22532,6 +22829,9 @@
       <c r="G326" t="s">
         <v>964</v>
       </c>
+      <c r="H326" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="327" spans="2:8">
       <c r="B327" t="s">
@@ -22549,6 +22849,9 @@
       <c r="G327" t="s">
         <v>964</v>
       </c>
+      <c r="H327" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="328" spans="2:8">
       <c r="B328" t="s">
@@ -22566,6 +22869,9 @@
       <c r="G328" t="s">
         <v>964</v>
       </c>
+      <c r="H328" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="329" spans="2:8">
       <c r="B329" t="s">
@@ -22583,6 +22889,9 @@
       <c r="G329" t="s">
         <v>964</v>
       </c>
+      <c r="H329" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="330" spans="2:8">
       <c r="B330" t="s">
@@ -22600,6 +22909,9 @@
       <c r="G330" t="s">
         <v>964</v>
       </c>
+      <c r="H330" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="331" spans="2:8">
       <c r="B331" t="s">
@@ -22657,6 +22969,9 @@
       <c r="G333" t="s">
         <v>964</v>
       </c>
+      <c r="H333" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="334" spans="2:8">
       <c r="B334" t="s">
@@ -22674,6 +22989,9 @@
       <c r="G334" t="s">
         <v>964</v>
       </c>
+      <c r="H334" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="335" spans="2:8">
       <c r="B335" t="s">
@@ -22691,6 +23009,9 @@
       <c r="G335" t="s">
         <v>964</v>
       </c>
+      <c r="H335" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="336" spans="2:8">
       <c r="B336" t="s">
@@ -22708,6 +23029,9 @@
       <c r="G336" t="s">
         <v>964</v>
       </c>
+      <c r="H336" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="337" spans="2:8">
       <c r="B337" t="s">
@@ -22725,6 +23049,9 @@
       <c r="G337" t="s">
         <v>964</v>
       </c>
+      <c r="H337" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="338" spans="2:8">
       <c r="B338" t="s">
@@ -22742,6 +23069,9 @@
       <c r="G338" t="s">
         <v>964</v>
       </c>
+      <c r="H338" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="339" spans="2:8">
       <c r="B339" t="s">
@@ -22759,6 +23089,9 @@
       <c r="G339" t="s">
         <v>964</v>
       </c>
+      <c r="H339" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="340" spans="2:8">
       <c r="B340" t="s">
@@ -22776,6 +23109,9 @@
       <c r="G340" t="s">
         <v>964</v>
       </c>
+      <c r="H340" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="341" spans="2:8">
       <c r="B341" t="s">
@@ -22793,6 +23129,9 @@
       <c r="G341" t="s">
         <v>964</v>
       </c>
+      <c r="H341" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="342" spans="2:8">
       <c r="B342" t="s">
@@ -22810,6 +23149,9 @@
       <c r="G342" t="s">
         <v>964</v>
       </c>
+      <c r="H342" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="343" spans="2:8">
       <c r="B343" t="s">
@@ -22827,6 +23169,9 @@
       <c r="G343" t="s">
         <v>964</v>
       </c>
+      <c r="H343" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="344" spans="2:8">
       <c r="B344" t="s">
@@ -22844,6 +23189,9 @@
       <c r="G344" t="s">
         <v>964</v>
       </c>
+      <c r="H344" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="345" spans="2:8">
       <c r="B345" t="s">
@@ -22861,6 +23209,9 @@
       <c r="G345" t="s">
         <v>964</v>
       </c>
+      <c r="H345" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="346" spans="2:8">
       <c r="B346" t="s">
@@ -22878,6 +23229,9 @@
       <c r="G346" t="s">
         <v>964</v>
       </c>
+      <c r="H346" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="347" spans="2:8">
       <c r="B347" t="s">
@@ -22895,6 +23249,9 @@
       <c r="G347" t="s">
         <v>964</v>
       </c>
+      <c r="H347" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="348" spans="2:8">
       <c r="B348" t="s">
@@ -22932,6 +23289,9 @@
       <c r="G349" t="s">
         <v>964</v>
       </c>
+      <c r="H349" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="350" spans="2:8">
       <c r="B350" t="s">
@@ -22949,6 +23309,9 @@
       <c r="G350" t="s">
         <v>964</v>
       </c>
+      <c r="H350" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="351" spans="2:8">
       <c r="B351" t="s">
@@ -22966,6 +23329,9 @@
       <c r="G351" t="s">
         <v>964</v>
       </c>
+      <c r="H351" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="352" spans="2:8">
       <c r="B352" t="s">
@@ -22983,6 +23349,9 @@
       <c r="G352" t="s">
         <v>964</v>
       </c>
+      <c r="H352" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="353" spans="2:8">
       <c r="B353" t="s">
@@ -23000,6 +23369,9 @@
       <c r="G353" t="s">
         <v>964</v>
       </c>
+      <c r="H353" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="354" spans="2:8">
       <c r="B354" t="s">
@@ -23017,6 +23389,9 @@
       <c r="G354" t="s">
         <v>964</v>
       </c>
+      <c r="H354" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="355" spans="2:8">
       <c r="B355" t="s">
@@ -23034,6 +23409,9 @@
       <c r="G355" t="s">
         <v>964</v>
       </c>
+      <c r="H355" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="356" spans="2:8">
       <c r="B356" t="s">
@@ -23051,6 +23429,9 @@
       <c r="G356" t="s">
         <v>964</v>
       </c>
+      <c r="H356" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="357" spans="2:8">
       <c r="B357" t="s">
@@ -23068,6 +23449,9 @@
       <c r="G357" t="s">
         <v>964</v>
       </c>
+      <c r="H357" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="358" spans="2:8">
       <c r="B358" t="s">
@@ -23085,6 +23469,9 @@
       <c r="G358" t="s">
         <v>964</v>
       </c>
+      <c r="H358" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="359" spans="2:8">
       <c r="B359" t="s">
@@ -23102,6 +23489,9 @@
       <c r="G359" t="s">
         <v>964</v>
       </c>
+      <c r="H359" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="360" spans="2:8">
       <c r="B360" t="s">
@@ -23119,6 +23509,9 @@
       <c r="G360" t="s">
         <v>964</v>
       </c>
+      <c r="H360" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="361" spans="2:8">
       <c r="B361" t="s">
@@ -23136,6 +23529,9 @@
       <c r="G361" t="s">
         <v>964</v>
       </c>
+      <c r="H361" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="362" spans="2:8">
       <c r="B362" t="s">
@@ -23153,6 +23549,9 @@
       <c r="G362" t="s">
         <v>964</v>
       </c>
+      <c r="H362" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="363" spans="2:8">
       <c r="B363" t="s">
@@ -23170,6 +23569,9 @@
       <c r="G363" t="s">
         <v>964</v>
       </c>
+      <c r="H363" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="364" spans="2:8">
       <c r="B364" t="s">
@@ -23187,6 +23589,9 @@
       <c r="G364" t="s">
         <v>964</v>
       </c>
+      <c r="H364" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="365" spans="2:8">
       <c r="B365" t="s">
@@ -23204,6 +23609,9 @@
       <c r="G365" t="s">
         <v>964</v>
       </c>
+      <c r="H365" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="366" spans="2:8">
       <c r="B366" t="s">
@@ -23242,7 +23650,7 @@
         <v>964</v>
       </c>
       <c r="H367" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="368" spans="2:8">
@@ -23261,8 +23669,11 @@
       <c r="G368" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="369" spans="2:7">
+      <c r="H368" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="369" spans="2:8">
       <c r="B369" t="s">
         <v>297</v>
       </c>
@@ -23278,8 +23689,11 @@
       <c r="G369" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="370" spans="2:7">
+      <c r="H369" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="370" spans="2:8">
       <c r="B370" t="s">
         <v>297</v>
       </c>
@@ -23295,8 +23709,11 @@
       <c r="G370" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="371" spans="2:7">
+      <c r="H370" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="371" spans="2:8">
       <c r="B371" t="s">
         <v>297</v>
       </c>
@@ -23312,8 +23729,11 @@
       <c r="G371" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="372" spans="2:7">
+      <c r="H371" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="372" spans="2:8">
       <c r="B372" t="s">
         <v>297</v>
       </c>
@@ -23329,8 +23749,11 @@
       <c r="G372" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="373" spans="2:7">
+      <c r="H372" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="373" spans="2:8">
       <c r="B373" t="s">
         <v>297</v>
       </c>
@@ -23346,8 +23769,11 @@
       <c r="G373" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="374" spans="2:7">
+      <c r="H373" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="374" spans="2:8">
       <c r="B374" t="s">
         <v>297</v>
       </c>
@@ -23363,8 +23789,11 @@
       <c r="G374" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="375" spans="2:7">
+      <c r="H374" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="375" spans="2:8">
       <c r="B375" t="s">
         <v>297</v>
       </c>
@@ -23380,8 +23809,11 @@
       <c r="G375" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="376" spans="2:7">
+      <c r="H375" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="376" spans="2:8">
       <c r="B376" t="s">
         <v>297</v>
       </c>
@@ -23397,8 +23829,11 @@
       <c r="G376" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="377" spans="2:7">
+      <c r="H376" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="377" spans="2:8">
       <c r="B377" t="s">
         <v>297</v>
       </c>
@@ -23414,8 +23849,11 @@
       <c r="G377" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="378" spans="2:7">
+      <c r="H377" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="378" spans="2:8">
       <c r="B378" t="s">
         <v>297</v>
       </c>
@@ -23431,8 +23869,11 @@
       <c r="G378" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="379" spans="2:7">
+      <c r="H378" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="379" spans="2:8">
       <c r="B379" t="s">
         <v>297</v>
       </c>
@@ -23448,8 +23889,11 @@
       <c r="G379" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="380" spans="2:7">
+      <c r="H379" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="380" spans="2:8">
       <c r="B380" t="s">
         <v>297</v>
       </c>
@@ -23465,8 +23909,11 @@
       <c r="G380" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="381" spans="2:7">
+      <c r="H380" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="381" spans="2:8">
       <c r="B381" t="s">
         <v>297</v>
       </c>
@@ -23482,8 +23929,11 @@
       <c r="G381" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="382" spans="2:7">
+      <c r="H381" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="382" spans="2:8">
       <c r="B382" t="s">
         <v>297</v>
       </c>
@@ -23499,8 +23949,11 @@
       <c r="G382" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="383" spans="2:7">
+      <c r="H382" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="383" spans="2:8">
       <c r="B383" t="s">
         <v>297</v>
       </c>
@@ -23516,8 +23969,11 @@
       <c r="G383" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="384" spans="2:7">
+      <c r="H383" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="384" spans="2:8">
       <c r="B384" t="s">
         <v>297</v>
       </c>
@@ -23533,6 +23989,9 @@
       <c r="G384" t="s">
         <v>964</v>
       </c>
+      <c r="H384" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="385" spans="2:8">
       <c r="B385" t="s">
@@ -23550,6 +24009,9 @@
       <c r="G385" t="s">
         <v>964</v>
       </c>
+      <c r="H385" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="386" spans="2:8">
       <c r="B386" t="s">
@@ -23567,6 +24029,9 @@
       <c r="G386" t="s">
         <v>964</v>
       </c>
+      <c r="H386" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="387" spans="2:8">
       <c r="B387" t="s">
@@ -23584,6 +24049,9 @@
       <c r="G387" t="s">
         <v>964</v>
       </c>
+      <c r="H387" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="388" spans="2:8">
       <c r="B388" t="s">
@@ -23601,6 +24069,9 @@
       <c r="G388" t="s">
         <v>964</v>
       </c>
+      <c r="H388" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="389" spans="2:8">
       <c r="B389" t="s">
@@ -23618,6 +24089,9 @@
       <c r="G389" t="s">
         <v>964</v>
       </c>
+      <c r="H389" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="390" spans="2:8">
       <c r="B390" t="s">
@@ -23656,7 +24130,7 @@
         <v>964</v>
       </c>
       <c r="H391" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="392" spans="2:8">
@@ -23675,6 +24149,9 @@
       <c r="G392" t="s">
         <v>964</v>
       </c>
+      <c r="H392" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="393" spans="2:8">
       <c r="B393" t="s">
@@ -23692,6 +24169,9 @@
       <c r="G393" t="s">
         <v>964</v>
       </c>
+      <c r="H393" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="394" spans="2:8">
       <c r="B394" t="s">
@@ -23709,6 +24189,9 @@
       <c r="G394" t="s">
         <v>964</v>
       </c>
+      <c r="H394" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="395" spans="2:8">
       <c r="B395" t="s">
@@ -23726,6 +24209,9 @@
       <c r="G395" t="s">
         <v>964</v>
       </c>
+      <c r="H395" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="396" spans="2:8">
       <c r="B396" t="s">
@@ -23743,6 +24229,9 @@
       <c r="G396" t="s">
         <v>964</v>
       </c>
+      <c r="H396" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="397" spans="2:8">
       <c r="B397" t="s">
@@ -23760,6 +24249,9 @@
       <c r="G397" t="s">
         <v>964</v>
       </c>
+      <c r="H397" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="398" spans="2:8">
       <c r="B398" t="s">
@@ -23777,6 +24269,9 @@
       <c r="G398" t="s">
         <v>964</v>
       </c>
+      <c r="H398" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="399" spans="2:8">
       <c r="B399" t="s">
@@ -23794,6 +24289,9 @@
       <c r="G399" t="s">
         <v>964</v>
       </c>
+      <c r="H399" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="400" spans="2:8">
       <c r="B400" t="s">
@@ -23811,6 +24309,9 @@
       <c r="G400" t="s">
         <v>964</v>
       </c>
+      <c r="H400" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="401" spans="2:8">
       <c r="B401" t="s">
@@ -23828,6 +24329,9 @@
       <c r="G401" t="s">
         <v>964</v>
       </c>
+      <c r="H401" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="402" spans="2:8">
       <c r="B402" t="s">
@@ -23845,6 +24349,9 @@
       <c r="G402" t="s">
         <v>964</v>
       </c>
+      <c r="H402" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="403" spans="2:8">
       <c r="B403" t="s">
@@ -23862,6 +24369,9 @@
       <c r="G403" t="s">
         <v>964</v>
       </c>
+      <c r="H403" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="404" spans="2:8">
       <c r="B404" t="s">
@@ -23879,6 +24389,9 @@
       <c r="G404" t="s">
         <v>964</v>
       </c>
+      <c r="H404" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="405" spans="2:8">
       <c r="B405" t="s">
@@ -23896,6 +24409,9 @@
       <c r="G405" t="s">
         <v>964</v>
       </c>
+      <c r="H405" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="406" spans="2:8">
       <c r="B406" t="s">
@@ -23913,6 +24429,9 @@
       <c r="G406" t="s">
         <v>964</v>
       </c>
+      <c r="H406" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="407" spans="2:8">
       <c r="B407" t="s">
@@ -23930,6 +24449,9 @@
       <c r="G407" t="s">
         <v>964</v>
       </c>
+      <c r="H407" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="408" spans="2:8">
       <c r="B408" t="s">
@@ -23947,6 +24469,9 @@
       <c r="G408" t="s">
         <v>964</v>
       </c>
+      <c r="H408" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="409" spans="2:8">
       <c r="B409" t="s">
@@ -23964,6 +24489,9 @@
       <c r="G409" t="s">
         <v>964</v>
       </c>
+      <c r="H409" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="410" spans="2:8">
       <c r="B410" t="s">
@@ -23981,6 +24509,9 @@
       <c r="G410" t="s">
         <v>964</v>
       </c>
+      <c r="H410" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="411" spans="2:8">
       <c r="B411" t="s">
@@ -24019,7 +24550,7 @@
         <v>964</v>
       </c>
       <c r="H412" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="413" spans="2:8">
@@ -24038,6 +24569,9 @@
       <c r="G413" t="s">
         <v>964</v>
       </c>
+      <c r="H413" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="414" spans="2:8">
       <c r="B414" t="s">
@@ -24055,6 +24589,9 @@
       <c r="G414" t="s">
         <v>964</v>
       </c>
+      <c r="H414" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="415" spans="2:8">
       <c r="B415" t="s">
@@ -24072,6 +24609,9 @@
       <c r="G415" t="s">
         <v>964</v>
       </c>
+      <c r="H415" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="416" spans="2:8">
       <c r="B416" t="s">
@@ -24089,6 +24629,9 @@
       <c r="G416" t="s">
         <v>964</v>
       </c>
+      <c r="H416" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="417" spans="2:8">
       <c r="B417" t="s">
@@ -24106,6 +24649,9 @@
       <c r="G417" t="s">
         <v>964</v>
       </c>
+      <c r="H417" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="418" spans="2:8">
       <c r="B418" t="s">
@@ -24123,6 +24669,9 @@
       <c r="G418" t="s">
         <v>964</v>
       </c>
+      <c r="H418" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="419" spans="2:8">
       <c r="B419" t="s">
@@ -24140,6 +24689,9 @@
       <c r="G419" t="s">
         <v>964</v>
       </c>
+      <c r="H419" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="420" spans="2:8">
       <c r="B420" t="s">
@@ -24157,6 +24709,9 @@
       <c r="G420" t="s">
         <v>964</v>
       </c>
+      <c r="H420" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="421" spans="2:8">
       <c r="B421" t="s">
@@ -24174,6 +24729,9 @@
       <c r="G421" t="s">
         <v>964</v>
       </c>
+      <c r="H421" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="422" spans="2:8">
       <c r="B422" t="s">
@@ -24191,6 +24749,9 @@
       <c r="G422" t="s">
         <v>964</v>
       </c>
+      <c r="H422" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="423" spans="2:8">
       <c r="B423" t="s">
@@ -24208,6 +24769,9 @@
       <c r="G423" t="s">
         <v>964</v>
       </c>
+      <c r="H423" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="424" spans="2:8">
       <c r="B424" t="s">
@@ -24225,6 +24789,9 @@
       <c r="G424" t="s">
         <v>964</v>
       </c>
+      <c r="H424" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="425" spans="2:8">
       <c r="B425" t="s">
@@ -24242,6 +24809,9 @@
       <c r="G425" t="s">
         <v>964</v>
       </c>
+      <c r="H425" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="426" spans="2:8">
       <c r="B426" t="s">
@@ -24259,6 +24829,9 @@
       <c r="G426" t="s">
         <v>964</v>
       </c>
+      <c r="H426" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="427" spans="2:8">
       <c r="B427" t="s">
@@ -24276,6 +24849,9 @@
       <c r="G427" t="s">
         <v>964</v>
       </c>
+      <c r="H427" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="428" spans="2:8">
       <c r="B428" t="s">
@@ -24293,6 +24869,9 @@
       <c r="G428" t="s">
         <v>964</v>
       </c>
+      <c r="H428" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="429" spans="2:8">
       <c r="B429" t="s">
@@ -24310,6 +24889,9 @@
       <c r="G429" t="s">
         <v>964</v>
       </c>
+      <c r="H429" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="430" spans="2:8">
       <c r="B430" t="s">
@@ -24327,6 +24909,9 @@
       <c r="G430" t="s">
         <v>964</v>
       </c>
+      <c r="H430" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="431" spans="2:8">
       <c r="B431" t="s">
@@ -24344,6 +24929,9 @@
       <c r="G431" t="s">
         <v>964</v>
       </c>
+      <c r="H431" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="432" spans="2:8">
       <c r="B432" t="s">
@@ -24362,10 +24950,10 @@
         <v>964</v>
       </c>
       <c r="H432" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="433" spans="2:7">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="433" spans="2:8">
       <c r="B433" t="s">
         <v>297</v>
       </c>
@@ -24381,8 +24969,11 @@
       <c r="G433" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="434" spans="2:7">
+      <c r="H433" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="434" spans="2:8">
       <c r="B434" t="s">
         <v>297</v>
       </c>
@@ -24398,8 +24989,11 @@
       <c r="G434" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="435" spans="2:7">
+      <c r="H434" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="435" spans="2:8">
       <c r="B435" t="s">
         <v>297</v>
       </c>
@@ -24415,8 +25009,11 @@
       <c r="G435" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="436" spans="2:7">
+      <c r="H435" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="436" spans="2:8">
       <c r="B436" t="s">
         <v>297</v>
       </c>
@@ -24432,8 +25029,11 @@
       <c r="G436" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="437" spans="2:7">
+      <c r="H436" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="437" spans="2:8">
       <c r="B437" t="s">
         <v>297</v>
       </c>
@@ -24449,8 +25049,11 @@
       <c r="G437" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="438" spans="2:7">
+      <c r="H437" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="438" spans="2:8">
       <c r="B438" t="s">
         <v>297</v>
       </c>
@@ -24466,8 +25069,11 @@
       <c r="G438" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="439" spans="2:7">
+      <c r="H438" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="439" spans="2:8">
       <c r="B439" t="s">
         <v>297</v>
       </c>
@@ -24483,8 +25089,11 @@
       <c r="G439" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="440" spans="2:7">
+      <c r="H439" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="440" spans="2:8">
       <c r="B440" t="s">
         <v>297</v>
       </c>
@@ -24500,8 +25109,11 @@
       <c r="G440" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="441" spans="2:7">
+      <c r="H440" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="441" spans="2:8">
       <c r="B441" t="s">
         <v>297</v>
       </c>
@@ -24517,8 +25129,11 @@
       <c r="G441" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="442" spans="2:7">
+      <c r="H441" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="442" spans="2:8">
       <c r="B442" t="s">
         <v>297</v>
       </c>
@@ -24534,8 +25149,11 @@
       <c r="G442" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="443" spans="2:7">
+      <c r="H442" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="443" spans="2:8">
       <c r="B443" t="s">
         <v>297</v>
       </c>
@@ -24551,8 +25169,11 @@
       <c r="G443" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="444" spans="2:7">
+      <c r="H443" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="444" spans="2:8">
       <c r="B444" t="s">
         <v>297</v>
       </c>
@@ -24568,8 +25189,11 @@
       <c r="G444" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="445" spans="2:7">
+      <c r="H444" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="445" spans="2:8">
       <c r="B445" t="s">
         <v>297</v>
       </c>
@@ -24585,8 +25209,11 @@
       <c r="G445" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="446" spans="2:7">
+      <c r="H445" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="446" spans="2:8">
       <c r="B446" t="s">
         <v>297</v>
       </c>
@@ -24602,8 +25229,11 @@
       <c r="G446" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="447" spans="2:7">
+      <c r="H446" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="447" spans="2:8">
       <c r="B447" t="s">
         <v>297</v>
       </c>
@@ -24619,8 +25249,11 @@
       <c r="G447" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="448" spans="2:7">
+      <c r="H447" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="448" spans="2:8">
       <c r="B448" t="s">
         <v>297</v>
       </c>
@@ -24636,8 +25269,11 @@
       <c r="G448" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="449" spans="2:7">
+      <c r="H448" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="449" spans="2:8">
       <c r="B449" t="s">
         <v>297</v>
       </c>
@@ -24653,8 +25289,11 @@
       <c r="G449" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="450" spans="2:7">
+      <c r="H449" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="450" spans="2:8">
       <c r="B450" t="s">
         <v>297</v>
       </c>
@@ -24670,8 +25309,11 @@
       <c r="G450" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="451" spans="2:7">
+      <c r="H450" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="451" spans="2:8">
       <c r="B451" t="s">
         <v>297</v>
       </c>
@@ -24687,8 +25329,11 @@
       <c r="G451" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="452" spans="2:7">
+      <c r="H451" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="452" spans="2:8">
       <c r="B452" t="s">
         <v>297</v>
       </c>
@@ -24704,8 +25349,11 @@
       <c r="G452" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="453" spans="2:7">
+      <c r="H452" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="453" spans="2:8">
       <c r="B453" t="s">
         <v>297</v>
       </c>
@@ -24721,8 +25369,11 @@
       <c r="G453" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="454" spans="2:7">
+      <c r="H453" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="454" spans="2:8">
       <c r="B454" t="s">
         <v>297</v>
       </c>
@@ -24738,8 +25389,11 @@
       <c r="G454" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="455" spans="2:7">
+      <c r="H454" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="455" spans="2:8">
       <c r="B455" t="s">
         <v>297</v>
       </c>
@@ -24755,8 +25409,11 @@
       <c r="G455" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="456" spans="2:7">
+      <c r="H455" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="456" spans="2:8">
       <c r="B456" t="s">
         <v>297</v>
       </c>
@@ -24772,8 +25429,11 @@
       <c r="G456" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="457" spans="2:7">
+      <c r="H456" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="457" spans="2:8">
       <c r="B457" t="s">
         <v>297</v>
       </c>
@@ -24789,8 +25449,11 @@
       <c r="G457" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="458" spans="2:7">
+      <c r="H457" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="458" spans="2:8">
       <c r="B458" t="s">
         <v>297</v>
       </c>
@@ -24806,8 +25469,11 @@
       <c r="G458" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="459" spans="2:7">
+      <c r="H458" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="459" spans="2:8">
       <c r="B459" t="s">
         <v>297</v>
       </c>
@@ -24823,8 +25489,11 @@
       <c r="G459" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="460" spans="2:7">
+      <c r="H459" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="460" spans="2:8">
       <c r="B460" t="s">
         <v>297</v>
       </c>
@@ -24840,8 +25509,11 @@
       <c r="G460" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="461" spans="2:7">
+      <c r="H460" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="461" spans="2:8">
       <c r="B461" t="s">
         <v>297</v>
       </c>
@@ -24857,8 +25529,11 @@
       <c r="G461" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="462" spans="2:7">
+      <c r="H461" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="462" spans="2:8">
       <c r="B462" t="s">
         <v>297</v>
       </c>
@@ -24874,8 +25549,11 @@
       <c r="G462" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="463" spans="2:7">
+      <c r="H462" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="463" spans="2:8">
       <c r="B463" t="s">
         <v>297</v>
       </c>
@@ -24891,8 +25569,11 @@
       <c r="G463" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="464" spans="2:7">
+      <c r="H463" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="464" spans="2:8">
       <c r="B464" t="s">
         <v>297</v>
       </c>
@@ -24908,6 +25589,9 @@
       <c r="G464" t="s">
         <v>964</v>
       </c>
+      <c r="H464" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="465" spans="2:8">
       <c r="B465" t="s">
@@ -24945,6 +25629,9 @@
       <c r="G466" t="s">
         <v>964</v>
       </c>
+      <c r="H466" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="467" spans="2:8">
       <c r="B467" t="s">
@@ -24962,6 +25649,9 @@
       <c r="G467" t="s">
         <v>964</v>
       </c>
+      <c r="H467" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="468" spans="2:8">
       <c r="B468" t="s">
@@ -24979,6 +25669,9 @@
       <c r="G468" t="s">
         <v>964</v>
       </c>
+      <c r="H468" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="469" spans="2:8">
       <c r="B469" t="s">
@@ -24996,6 +25689,9 @@
       <c r="G469" t="s">
         <v>964</v>
       </c>
+      <c r="H469" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="470" spans="2:8">
       <c r="B470" t="s">
@@ -25013,6 +25709,9 @@
       <c r="G470" t="s">
         <v>964</v>
       </c>
+      <c r="H470" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="471" spans="2:8">
       <c r="B471" t="s">
@@ -25030,6 +25729,9 @@
       <c r="G471" t="s">
         <v>964</v>
       </c>
+      <c r="H471" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="472" spans="2:8">
       <c r="B472" t="s">
@@ -25047,6 +25749,9 @@
       <c r="G472" t="s">
         <v>964</v>
       </c>
+      <c r="H472" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="473" spans="2:8">
       <c r="B473" t="s">
@@ -25064,6 +25769,9 @@
       <c r="G473" t="s">
         <v>964</v>
       </c>
+      <c r="H473" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="474" spans="2:8">
       <c r="B474" t="s">
@@ -25081,6 +25789,9 @@
       <c r="G474" t="s">
         <v>964</v>
       </c>
+      <c r="H474" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="475" spans="2:8">
       <c r="B475" t="s">
@@ -25098,6 +25809,9 @@
       <c r="G475" t="s">
         <v>964</v>
       </c>
+      <c r="H475" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="476" spans="2:8">
       <c r="B476" t="s">
@@ -25115,6 +25829,9 @@
       <c r="G476" t="s">
         <v>964</v>
       </c>
+      <c r="H476" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="477" spans="2:8">
       <c r="B477" t="s">
@@ -25132,6 +25849,9 @@
       <c r="G477" t="s">
         <v>964</v>
       </c>
+      <c r="H477" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="478" spans="2:8">
       <c r="B478" t="s">
@@ -25149,6 +25869,9 @@
       <c r="G478" t="s">
         <v>964</v>
       </c>
+      <c r="H478" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="479" spans="2:8">
       <c r="B479" t="s">
@@ -25186,6 +25909,9 @@
       <c r="G480" t="s">
         <v>964</v>
       </c>
+      <c r="H480" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="481" spans="2:8">
       <c r="B481" t="s">
@@ -25203,6 +25929,9 @@
       <c r="G481" t="s">
         <v>964</v>
       </c>
+      <c r="H481" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="482" spans="2:8">
       <c r="B482" t="s">
@@ -25220,6 +25949,9 @@
       <c r="G482" t="s">
         <v>964</v>
       </c>
+      <c r="H482" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="483" spans="2:8">
       <c r="B483" t="s">
@@ -25237,6 +25969,9 @@
       <c r="G483" t="s">
         <v>964</v>
       </c>
+      <c r="H483" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="484" spans="2:8">
       <c r="B484" t="s">
@@ -25254,6 +25989,9 @@
       <c r="G484" t="s">
         <v>964</v>
       </c>
+      <c r="H484" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="485" spans="2:8">
       <c r="B485" t="s">
@@ -25271,6 +26009,9 @@
       <c r="G485" t="s">
         <v>964</v>
       </c>
+      <c r="H485" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="486" spans="2:8">
       <c r="B486" t="s">
@@ -25288,6 +26029,9 @@
       <c r="G486" t="s">
         <v>964</v>
       </c>
+      <c r="H486" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="487" spans="2:8">
       <c r="B487" t="s">
@@ -25305,6 +26049,9 @@
       <c r="G487" t="s">
         <v>964</v>
       </c>
+      <c r="H487" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="488" spans="2:8">
       <c r="B488" t="s">
@@ -25322,6 +26069,9 @@
       <c r="G488" t="s">
         <v>964</v>
       </c>
+      <c r="H488" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="489" spans="2:8">
       <c r="B489" t="s">
@@ -25339,6 +26089,9 @@
       <c r="G489" t="s">
         <v>964</v>
       </c>
+      <c r="H489" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="490" spans="2:8">
       <c r="B490" t="s">
@@ -25356,6 +26109,9 @@
       <c r="G490" t="s">
         <v>964</v>
       </c>
+      <c r="H490" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="491" spans="2:8">
       <c r="B491" t="s">
@@ -25373,6 +26129,9 @@
       <c r="G491" t="s">
         <v>964</v>
       </c>
+      <c r="H491" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="492" spans="2:8">
       <c r="B492" t="s">
@@ -25390,6 +26149,9 @@
       <c r="G492" t="s">
         <v>964</v>
       </c>
+      <c r="H492" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="493" spans="2:8">
       <c r="B493" t="s">
@@ -25407,6 +26169,9 @@
       <c r="G493" t="s">
         <v>964</v>
       </c>
+      <c r="H493" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="494" spans="2:8">
       <c r="B494" t="s">
@@ -25424,6 +26189,9 @@
       <c r="G494" t="s">
         <v>964</v>
       </c>
+      <c r="H494" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="495" spans="2:8">
       <c r="B495" t="s">
@@ -25442,7 +26210,7 @@
         <v>964</v>
       </c>
       <c r="H495" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="496" spans="2:8">
@@ -25461,6 +26229,9 @@
       <c r="G496" t="s">
         <v>964</v>
       </c>
+      <c r="H496" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="497" spans="2:8">
       <c r="B497" t="s">
@@ -25478,6 +26249,9 @@
       <c r="G497" t="s">
         <v>964</v>
       </c>
+      <c r="H497" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="498" spans="2:8">
       <c r="B498" t="s">
@@ -25495,6 +26269,9 @@
       <c r="G498" t="s">
         <v>964</v>
       </c>
+      <c r="H498" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="499" spans="2:8">
       <c r="B499" t="s">
@@ -25512,6 +26289,9 @@
       <c r="G499" t="s">
         <v>964</v>
       </c>
+      <c r="H499" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="500" spans="2:8">
       <c r="B500" t="s">
@@ -25529,6 +26309,9 @@
       <c r="G500" t="s">
         <v>964</v>
       </c>
+      <c r="H500" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="501" spans="2:8">
       <c r="B501" t="s">
@@ -25546,6 +26329,9 @@
       <c r="G501" t="s">
         <v>964</v>
       </c>
+      <c r="H501" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="502" spans="2:8">
       <c r="B502" t="s">
@@ -25623,6 +26409,9 @@
       <c r="G505" t="s">
         <v>964</v>
       </c>
+      <c r="H505" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="506" spans="2:8">
       <c r="B506" t="s">
@@ -25640,6 +26429,9 @@
       <c r="G506" t="s">
         <v>964</v>
       </c>
+      <c r="H506" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="507" spans="2:8">
       <c r="B507" t="s">
@@ -25657,6 +26449,9 @@
       <c r="G507" t="s">
         <v>964</v>
       </c>
+      <c r="H507" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="508" spans="2:8">
       <c r="B508" t="s">
@@ -25674,6 +26469,9 @@
       <c r="G508" t="s">
         <v>964</v>
       </c>
+      <c r="H508" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="509" spans="2:8">
       <c r="B509" t="s">
@@ -25691,6 +26489,9 @@
       <c r="G509" t="s">
         <v>964</v>
       </c>
+      <c r="H509" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="510" spans="2:8">
       <c r="B510" t="s">
@@ -25708,6 +26509,9 @@
       <c r="G510" t="s">
         <v>964</v>
       </c>
+      <c r="H510" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="511" spans="2:8">
       <c r="B511" t="s">
@@ -25725,6 +26529,9 @@
       <c r="G511" t="s">
         <v>964</v>
       </c>
+      <c r="H511" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="512" spans="2:8">
       <c r="B512" t="s">
@@ -25742,6 +26549,9 @@
       <c r="G512" t="s">
         <v>964</v>
       </c>
+      <c r="H512" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="513" spans="2:8">
       <c r="B513" t="s">
@@ -25759,6 +26569,9 @@
       <c r="G513" t="s">
         <v>964</v>
       </c>
+      <c r="H513" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="514" spans="2:8">
       <c r="B514" t="s">
@@ -25776,6 +26589,9 @@
       <c r="G514" t="s">
         <v>964</v>
       </c>
+      <c r="H514" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="515" spans="2:8">
       <c r="B515" t="s">
@@ -25793,6 +26609,9 @@
       <c r="G515" t="s">
         <v>964</v>
       </c>
+      <c r="H515" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="516" spans="2:8">
       <c r="B516" t="s">
@@ -25810,6 +26629,9 @@
       <c r="G516" t="s">
         <v>964</v>
       </c>
+      <c r="H516" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="517" spans="2:8">
       <c r="B517" t="s">
@@ -25847,6 +26669,9 @@
       <c r="G518" t="s">
         <v>964</v>
       </c>
+      <c r="H518" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="519" spans="2:8">
       <c r="B519" t="s">
@@ -25864,6 +26689,9 @@
       <c r="G519" t="s">
         <v>964</v>
       </c>
+      <c r="H519" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="520" spans="2:8">
       <c r="B520" t="s">
@@ -25941,6 +26769,9 @@
       <c r="G523" t="s">
         <v>964</v>
       </c>
+      <c r="H523" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="524" spans="2:8">
       <c r="B524" t="s">
@@ -25958,6 +26789,9 @@
       <c r="G524" t="s">
         <v>964</v>
       </c>
+      <c r="H524" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="525" spans="2:8">
       <c r="B525" t="s">
@@ -25975,6 +26809,9 @@
       <c r="G525" t="s">
         <v>964</v>
       </c>
+      <c r="H525" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="526" spans="2:8">
       <c r="B526" t="s">
@@ -25992,6 +26829,9 @@
       <c r="G526" t="s">
         <v>964</v>
       </c>
+      <c r="H526" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="527" spans="2:8">
       <c r="B527" t="s">
@@ -26009,6 +26849,9 @@
       <c r="G527" t="s">
         <v>964</v>
       </c>
+      <c r="H527" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="528" spans="2:8">
       <c r="B528" t="s">
@@ -26026,6 +26869,9 @@
       <c r="G528" t="s">
         <v>964</v>
       </c>
+      <c r="H528" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="529" spans="2:8">
       <c r="B529" t="s">
@@ -26043,6 +26889,9 @@
       <c r="G529" t="s">
         <v>964</v>
       </c>
+      <c r="H529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="530" spans="2:8">
       <c r="B530" t="s">
@@ -26060,6 +26909,9 @@
       <c r="G530" t="s">
         <v>964</v>
       </c>
+      <c r="H530" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="531" spans="2:8">
       <c r="B531" t="s">
@@ -26077,6 +26929,9 @@
       <c r="G531" t="s">
         <v>964</v>
       </c>
+      <c r="H531" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="532" spans="2:8">
       <c r="B532" t="s">
@@ -26094,6 +26949,9 @@
       <c r="G532" t="s">
         <v>964</v>
       </c>
+      <c r="H532" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="533" spans="2:8">
       <c r="B533" t="s">
@@ -26111,6 +26969,9 @@
       <c r="G533" t="s">
         <v>964</v>
       </c>
+      <c r="H533" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="534" spans="2:8">
       <c r="B534" t="s">
@@ -26128,6 +26989,9 @@
       <c r="G534" t="s">
         <v>964</v>
       </c>
+      <c r="H534" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="535" spans="2:8">
       <c r="B535" t="s">
@@ -26145,6 +27009,9 @@
       <c r="G535" t="s">
         <v>964</v>
       </c>
+      <c r="H535" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="536" spans="2:8">
       <c r="B536" t="s">
@@ -26162,6 +27029,9 @@
       <c r="G536" t="s">
         <v>964</v>
       </c>
+      <c r="H536" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="537" spans="2:8">
       <c r="B537" t="s">
@@ -26239,6 +27109,9 @@
       <c r="G540" t="s">
         <v>964</v>
       </c>
+      <c r="H540" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="541" spans="2:8">
       <c r="B541" t="s">
@@ -26256,6 +27129,9 @@
       <c r="G541" t="s">
         <v>964</v>
       </c>
+      <c r="H541" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="542" spans="2:8">
       <c r="B542" t="s">
@@ -26273,6 +27149,9 @@
       <c r="G542" t="s">
         <v>964</v>
       </c>
+      <c r="H542" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="543" spans="2:8">
       <c r="B543" t="s">
@@ -26290,6 +27169,9 @@
       <c r="G543" t="s">
         <v>964</v>
       </c>
+      <c r="H543" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="544" spans="2:8">
       <c r="B544" t="s">
@@ -26307,6 +27189,9 @@
       <c r="G544" t="s">
         <v>964</v>
       </c>
+      <c r="H544" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="545" spans="2:8">
       <c r="B545" t="s">
@@ -26324,6 +27209,9 @@
       <c r="G545" t="s">
         <v>964</v>
       </c>
+      <c r="H545" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="546" spans="2:8">
       <c r="B546" t="s">
@@ -26341,6 +27229,9 @@
       <c r="G546" t="s">
         <v>964</v>
       </c>
+      <c r="H546" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="547" spans="2:8">
       <c r="B547" t="s">
@@ -26358,6 +27249,9 @@
       <c r="G547" t="s">
         <v>964</v>
       </c>
+      <c r="H547" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="548" spans="2:8">
       <c r="B548" t="s">
@@ -26375,6 +27269,9 @@
       <c r="G548" t="s">
         <v>964</v>
       </c>
+      <c r="H548" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="549" spans="2:8">
       <c r="B549" t="s">
@@ -26392,6 +27289,9 @@
       <c r="G549" t="s">
         <v>964</v>
       </c>
+      <c r="H549" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="550" spans="2:8">
       <c r="B550" t="s">
@@ -26409,6 +27309,9 @@
       <c r="G550" t="s">
         <v>964</v>
       </c>
+      <c r="H550" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="551" spans="2:8">
       <c r="B551" t="s">
@@ -26426,6 +27329,9 @@
       <c r="G551" t="s">
         <v>964</v>
       </c>
+      <c r="H551" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="552" spans="2:8">
       <c r="B552" t="s">
@@ -26443,6 +27349,9 @@
       <c r="G552" t="s">
         <v>964</v>
       </c>
+      <c r="H552" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="553" spans="2:8">
       <c r="B553" t="s">
@@ -26460,6 +27369,9 @@
       <c r="G553" t="s">
         <v>964</v>
       </c>
+      <c r="H553" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="554" spans="2:8">
       <c r="B554" t="s">
@@ -26517,6 +27429,9 @@
       <c r="G556" t="s">
         <v>964</v>
       </c>
+      <c r="H556" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="557" spans="2:8">
       <c r="B557" t="s">
@@ -26534,6 +27449,9 @@
       <c r="G557" t="s">
         <v>964</v>
       </c>
+      <c r="H557" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="558" spans="2:8">
       <c r="B558" t="s">
@@ -26551,6 +27469,9 @@
       <c r="G558" t="s">
         <v>964</v>
       </c>
+      <c r="H558" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="559" spans="2:8">
       <c r="B559" t="s">
@@ -26568,6 +27489,9 @@
       <c r="G559" t="s">
         <v>964</v>
       </c>
+      <c r="H559" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="560" spans="2:8">
       <c r="B560" t="s">
@@ -26585,8 +27509,11 @@
       <c r="G560" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="561" spans="2:7">
+      <c r="H560" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="561" spans="2:8">
       <c r="B561" t="s">
         <v>297</v>
       </c>
@@ -26602,8 +27529,11 @@
       <c r="G561" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="562" spans="2:7">
+      <c r="H561" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="562" spans="2:8">
       <c r="B562" t="s">
         <v>297</v>
       </c>
@@ -26619,8 +27549,11 @@
       <c r="G562" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="563" spans="2:7">
+      <c r="H562" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="563" spans="2:8">
       <c r="B563" t="s">
         <v>297</v>
       </c>
@@ -26636,8 +27569,11 @@
       <c r="G563" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="564" spans="2:7">
+      <c r="H563" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="564" spans="2:8">
       <c r="B564" t="s">
         <v>297</v>
       </c>
@@ -26653,8 +27589,11 @@
       <c r="G564" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="565" spans="2:7">
+      <c r="H564" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="565" spans="2:8">
       <c r="B565" t="s">
         <v>297</v>
       </c>
@@ -26670,8 +27609,11 @@
       <c r="G565" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="566" spans="2:7">
+      <c r="H565" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="566" spans="2:8">
       <c r="B566" t="s">
         <v>297</v>
       </c>
@@ -26687,8 +27629,11 @@
       <c r="G566" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="567" spans="2:7">
+      <c r="H566" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="567" spans="2:8">
       <c r="B567" t="s">
         <v>297</v>
       </c>
@@ -26704,8 +27649,11 @@
       <c r="G567" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="568" spans="2:7">
+      <c r="H567" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="568" spans="2:8">
       <c r="B568" t="s">
         <v>297</v>
       </c>
@@ -26721,8 +27669,11 @@
       <c r="G568" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="569" spans="2:7">
+      <c r="H568" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="569" spans="2:8">
       <c r="B569" t="s">
         <v>297</v>
       </c>
@@ -26738,8 +27689,11 @@
       <c r="G569" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="570" spans="2:7">
+      <c r="H569" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="570" spans="2:8">
       <c r="B570" t="s">
         <v>297</v>
       </c>
@@ -26755,8 +27709,11 @@
       <c r="G570" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="571" spans="2:7">
+      <c r="H570" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="571" spans="2:8">
       <c r="B571" t="s">
         <v>297</v>
       </c>
@@ -26772,8 +27729,11 @@
       <c r="G571" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="572" spans="2:7">
+      <c r="H571" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="572" spans="2:8">
       <c r="B572" t="s">
         <v>297</v>
       </c>
@@ -26789,8 +27749,11 @@
       <c r="G572" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="573" spans="2:7">
+      <c r="H572" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="573" spans="2:8">
       <c r="B573" t="s">
         <v>297</v>
       </c>
@@ -26806,8 +27769,11 @@
       <c r="G573" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="574" spans="2:7">
+      <c r="H573" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="574" spans="2:8">
       <c r="B574" t="s">
         <v>297</v>
       </c>
@@ -26823,8 +27789,11 @@
       <c r="G574" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="575" spans="2:7">
+      <c r="H574" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="575" spans="2:8">
       <c r="B575" t="s">
         <v>297</v>
       </c>
@@ -26840,8 +27809,11 @@
       <c r="G575" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="576" spans="2:7">
+      <c r="H575" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="576" spans="2:8">
       <c r="B576" t="s">
         <v>297</v>
       </c>
@@ -26857,6 +27829,9 @@
       <c r="G576" t="s">
         <v>964</v>
       </c>
+      <c r="H576" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="577" spans="2:8">
       <c r="B577" t="s">
@@ -26874,6 +27849,9 @@
       <c r="G577" t="s">
         <v>964</v>
       </c>
+      <c r="H577" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="578" spans="2:8">
       <c r="B578" t="s">
@@ -26891,6 +27869,9 @@
       <c r="G578" t="s">
         <v>964</v>
       </c>
+      <c r="H578" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="579" spans="2:8">
       <c r="B579" t="s">
@@ -26908,6 +27889,9 @@
       <c r="G579" t="s">
         <v>964</v>
       </c>
+      <c r="H579" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="580" spans="2:8">
       <c r="B580" t="s">
@@ -26925,6 +27909,9 @@
       <c r="G580" t="s">
         <v>964</v>
       </c>
+      <c r="H580" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="581" spans="2:8">
       <c r="B581" t="s">
@@ -26942,6 +27929,9 @@
       <c r="G581" t="s">
         <v>964</v>
       </c>
+      <c r="H581" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="582" spans="2:8">
       <c r="B582" t="s">
@@ -26959,6 +27949,9 @@
       <c r="G582" t="s">
         <v>964</v>
       </c>
+      <c r="H582" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="583" spans="2:8">
       <c r="B583" t="s">
@@ -26976,6 +27969,9 @@
       <c r="G583" t="s">
         <v>964</v>
       </c>
+      <c r="H583" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="584" spans="2:8">
       <c r="B584" t="s">
@@ -26993,6 +27989,9 @@
       <c r="G584" t="s">
         <v>964</v>
       </c>
+      <c r="H584" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="585" spans="2:8">
       <c r="B585" t="s">
@@ -27010,6 +28009,9 @@
       <c r="G585" t="s">
         <v>964</v>
       </c>
+      <c r="H585" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="586" spans="2:8">
       <c r="B586" t="s">
@@ -27028,7 +28030,7 @@
         <v>964</v>
       </c>
       <c r="H586" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="587" spans="2:8">
@@ -27048,7 +28050,7 @@
         <v>964</v>
       </c>
       <c r="H587" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="588" spans="2:8">
@@ -27087,6 +28089,9 @@
       <c r="G589" t="s">
         <v>964</v>
       </c>
+      <c r="H589" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="590" spans="2:8">
       <c r="B590" t="s">
@@ -27104,6 +28109,9 @@
       <c r="G590" t="s">
         <v>964</v>
       </c>
+      <c r="H590" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="591" spans="2:8">
       <c r="B591" t="s">
@@ -27121,6 +28129,9 @@
       <c r="G591" t="s">
         <v>964</v>
       </c>
+      <c r="H591" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="592" spans="2:8">
       <c r="B592" t="s">
@@ -27138,8 +28149,11 @@
       <c r="G592" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="593" spans="2:7">
+      <c r="H592" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="593" spans="2:8">
       <c r="B593" t="s">
         <v>297</v>
       </c>
@@ -27155,8 +28169,11 @@
       <c r="G593" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="594" spans="2:7">
+      <c r="H593" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="594" spans="2:8">
       <c r="B594" t="s">
         <v>297</v>
       </c>
@@ -27172,8 +28189,11 @@
       <c r="G594" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="595" spans="2:7">
+      <c r="H594" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="595" spans="2:8">
       <c r="B595" t="s">
         <v>297</v>
       </c>
@@ -27189,8 +28209,11 @@
       <c r="G595" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="596" spans="2:7">
+      <c r="H595" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="596" spans="2:8">
       <c r="B596" t="s">
         <v>297</v>
       </c>
@@ -27206,8 +28229,11 @@
       <c r="G596" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="597" spans="2:7">
+      <c r="H596" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="597" spans="2:8">
       <c r="B597" t="s">
         <v>297</v>
       </c>
@@ -27223,8 +28249,11 @@
       <c r="G597" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="598" spans="2:7">
+      <c r="H597" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="598" spans="2:8">
       <c r="B598" t="s">
         <v>297</v>
       </c>
@@ -27240,8 +28269,11 @@
       <c r="G598" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="599" spans="2:7">
+      <c r="H598" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="599" spans="2:8">
       <c r="B599" t="s">
         <v>297</v>
       </c>
@@ -27257,8 +28289,11 @@
       <c r="G599" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="600" spans="2:7">
+      <c r="H599" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="600" spans="2:8">
       <c r="B600" t="s">
         <v>297</v>
       </c>
@@ -27274,8 +28309,11 @@
       <c r="G600" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="601" spans="2:7">
+      <c r="H600" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="601" spans="2:8">
       <c r="B601" t="s">
         <v>297</v>
       </c>
@@ -27291,8 +28329,11 @@
       <c r="G601" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="602" spans="2:7">
+      <c r="H601" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="602" spans="2:8">
       <c r="B602" t="s">
         <v>297</v>
       </c>
@@ -27308,8 +28349,11 @@
       <c r="G602" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="603" spans="2:7">
+      <c r="H602" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="603" spans="2:8">
       <c r="B603" t="s">
         <v>297</v>
       </c>
@@ -27325,8 +28369,11 @@
       <c r="G603" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="604" spans="2:7">
+      <c r="H603" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="604" spans="2:8">
       <c r="B604" t="s">
         <v>297</v>
       </c>
@@ -27342,8 +28389,11 @@
       <c r="G604" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="605" spans="2:7">
+      <c r="H604" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="605" spans="2:8">
       <c r="B605" t="s">
         <v>297</v>
       </c>
@@ -27359,8 +28409,11 @@
       <c r="G605" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="606" spans="2:7">
+      <c r="H605" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="606" spans="2:8">
       <c r="B606" t="s">
         <v>297</v>
       </c>
@@ -27376,8 +28429,11 @@
       <c r="G606" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="607" spans="2:7">
+      <c r="H606" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="607" spans="2:8">
       <c r="B607" t="s">
         <v>297</v>
       </c>
@@ -27393,8 +28449,11 @@
       <c r="G607" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="608" spans="2:7">
+      <c r="H607" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="608" spans="2:8">
       <c r="B608" t="s">
         <v>297</v>
       </c>
@@ -27410,8 +28469,11 @@
       <c r="G608" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="609" spans="2:7">
+      <c r="H608" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="609" spans="2:8">
       <c r="B609" t="s">
         <v>297</v>
       </c>
@@ -27427,8 +28489,11 @@
       <c r="G609" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="610" spans="2:7">
+      <c r="H609" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="610" spans="2:8">
       <c r="B610" t="s">
         <v>297</v>
       </c>
@@ -27444,8 +28509,11 @@
       <c r="G610" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="611" spans="2:7">
+      <c r="H610" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="611" spans="2:8">
       <c r="B611" t="s">
         <v>297</v>
       </c>
@@ -27461,8 +28529,11 @@
       <c r="G611" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="612" spans="2:7">
+      <c r="H611" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="612" spans="2:8">
       <c r="B612" t="s">
         <v>297</v>
       </c>
@@ -27478,8 +28549,11 @@
       <c r="G612" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="613" spans="2:7">
+      <c r="H612" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="613" spans="2:8">
       <c r="B613" t="s">
         <v>297</v>
       </c>
@@ -27495,8 +28569,11 @@
       <c r="G613" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="614" spans="2:7">
+      <c r="H613" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="614" spans="2:8">
       <c r="B614" t="s">
         <v>297</v>
       </c>
@@ -27512,8 +28589,11 @@
       <c r="G614" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="615" spans="2:7">
+      <c r="H614" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="615" spans="2:8">
       <c r="B615" t="s">
         <v>297</v>
       </c>
@@ -27529,8 +28609,11 @@
       <c r="G615" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="616" spans="2:7">
+      <c r="H615" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="616" spans="2:8">
       <c r="B616" t="s">
         <v>297</v>
       </c>
@@ -27546,8 +28629,11 @@
       <c r="G616" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="617" spans="2:7">
+      <c r="H616" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="617" spans="2:8">
       <c r="B617" t="s">
         <v>297</v>
       </c>
@@ -27563,8 +28649,11 @@
       <c r="G617" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="618" spans="2:7">
+      <c r="H617" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="618" spans="2:8">
       <c r="B618" t="s">
         <v>297</v>
       </c>
@@ -27580,8 +28669,11 @@
       <c r="G618" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="619" spans="2:7">
+      <c r="H618" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="619" spans="2:8">
       <c r="B619" t="s">
         <v>297</v>
       </c>
@@ -27597,8 +28689,11 @@
       <c r="G619" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="620" spans="2:7">
+      <c r="H619" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="620" spans="2:8">
       <c r="B620" t="s">
         <v>297</v>
       </c>
@@ -27614,8 +28709,11 @@
       <c r="G620" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="621" spans="2:7">
+      <c r="H620" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="621" spans="2:8">
       <c r="B621" t="s">
         <v>297</v>
       </c>
@@ -27631,8 +28729,11 @@
       <c r="G621" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="622" spans="2:7">
+      <c r="H621" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="622" spans="2:8">
       <c r="B622" t="s">
         <v>297</v>
       </c>
@@ -27648,8 +28749,11 @@
       <c r="G622" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="623" spans="2:7">
+      <c r="H622" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="623" spans="2:8">
       <c r="B623" t="s">
         <v>297</v>
       </c>
@@ -27665,8 +28769,11 @@
       <c r="G623" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="624" spans="2:7">
+      <c r="H623" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="624" spans="2:8">
       <c r="B624" t="s">
         <v>297</v>
       </c>
@@ -27682,8 +28789,11 @@
       <c r="G624" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="625" spans="2:7">
+      <c r="H624" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="625" spans="2:8">
       <c r="B625" t="s">
         <v>297</v>
       </c>
@@ -27699,8 +28809,11 @@
       <c r="G625" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="626" spans="2:7">
+      <c r="H625" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="626" spans="2:8">
       <c r="B626" t="s">
         <v>297</v>
       </c>
@@ -27716,8 +28829,11 @@
       <c r="G626" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="627" spans="2:7">
+      <c r="H626" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="627" spans="2:8">
       <c r="B627" t="s">
         <v>297</v>
       </c>
@@ -27733,8 +28849,11 @@
       <c r="G627" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="628" spans="2:7">
+      <c r="H627" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="628" spans="2:8">
       <c r="B628" t="s">
         <v>297</v>
       </c>
@@ -27750,8 +28869,11 @@
       <c r="G628" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="629" spans="2:7">
+      <c r="H628" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="629" spans="2:8">
       <c r="B629" t="s">
         <v>297</v>
       </c>
@@ -27767,8 +28889,11 @@
       <c r="G629" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="630" spans="2:7">
+      <c r="H629" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="630" spans="2:8">
       <c r="B630" t="s">
         <v>297</v>
       </c>
@@ -27784,8 +28909,11 @@
       <c r="G630" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="631" spans="2:7">
+      <c r="H630" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="631" spans="2:8">
       <c r="B631" t="s">
         <v>297</v>
       </c>
@@ -27801,8 +28929,11 @@
       <c r="G631" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="632" spans="2:7">
+      <c r="H631" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="632" spans="2:8">
       <c r="B632" t="s">
         <v>297</v>
       </c>
@@ -27818,8 +28949,11 @@
       <c r="G632" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="633" spans="2:7">
+      <c r="H632" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="633" spans="2:8">
       <c r="B633" t="s">
         <v>297</v>
       </c>
@@ -27835,8 +28969,11 @@
       <c r="G633" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="634" spans="2:7">
+      <c r="H633" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="634" spans="2:8">
       <c r="B634" t="s">
         <v>297</v>
       </c>
@@ -27852,8 +28989,11 @@
       <c r="G634" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="635" spans="2:7">
+      <c r="H634" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="635" spans="2:8">
       <c r="B635" t="s">
         <v>297</v>
       </c>
@@ -27869,8 +29009,11 @@
       <c r="G635" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="636" spans="2:7">
+      <c r="H635" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="636" spans="2:8">
       <c r="B636" t="s">
         <v>297</v>
       </c>
@@ -27886,8 +29029,11 @@
       <c r="G636" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="637" spans="2:7">
+      <c r="H636" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="637" spans="2:8">
       <c r="B637" t="s">
         <v>297</v>
       </c>
@@ -27903,8 +29049,11 @@
       <c r="G637" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="638" spans="2:7">
+      <c r="H637" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="638" spans="2:8">
       <c r="B638" t="s">
         <v>297</v>
       </c>
@@ -27920,8 +29069,11 @@
       <c r="G638" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="639" spans="2:7">
+      <c r="H638" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="639" spans="2:8">
       <c r="B639" t="s">
         <v>297</v>
       </c>
@@ -27937,8 +29089,11 @@
       <c r="G639" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="640" spans="2:7">
+      <c r="H639" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="640" spans="2:8">
       <c r="B640" t="s">
         <v>297</v>
       </c>
@@ -27954,8 +29109,11 @@
       <c r="G640" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="641" spans="2:7">
+      <c r="H640" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="641" spans="2:8">
       <c r="B641" t="s">
         <v>297</v>
       </c>
@@ -27971,8 +29129,11 @@
       <c r="G641" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="642" spans="2:7">
+      <c r="H641" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="642" spans="2:8">
       <c r="B642" t="s">
         <v>297</v>
       </c>
@@ -27988,8 +29149,11 @@
       <c r="G642" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="643" spans="2:7">
+      <c r="H642" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="643" spans="2:8">
       <c r="B643" t="s">
         <v>297</v>
       </c>
@@ -28005,8 +29169,11 @@
       <c r="G643" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="644" spans="2:7">
+      <c r="H643" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="644" spans="2:8">
       <c r="B644" t="s">
         <v>297</v>
       </c>
@@ -28022,8 +29189,11 @@
       <c r="G644" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="645" spans="2:7">
+      <c r="H644" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="645" spans="2:8">
       <c r="B645" t="s">
         <v>297</v>
       </c>
@@ -28039,8 +29209,11 @@
       <c r="G645" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="646" spans="2:7">
+      <c r="H645" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="646" spans="2:8">
       <c r="B646" t="s">
         <v>297</v>
       </c>
@@ -28056,8 +29229,11 @@
       <c r="G646" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="647" spans="2:7">
+      <c r="H646" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="647" spans="2:8">
       <c r="B647" t="s">
         <v>297</v>
       </c>
@@ -28073,8 +29249,11 @@
       <c r="G647" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="648" spans="2:7">
+      <c r="H647" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="648" spans="2:8">
       <c r="B648" t="s">
         <v>297</v>
       </c>
@@ -28090,8 +29269,11 @@
       <c r="G648" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="649" spans="2:7">
+      <c r="H648" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="649" spans="2:8">
       <c r="B649" t="s">
         <v>297</v>
       </c>
@@ -28107,8 +29289,11 @@
       <c r="G649" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="650" spans="2:7">
+      <c r="H649" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="650" spans="2:8">
       <c r="B650" t="s">
         <v>297</v>
       </c>
@@ -28124,8 +29309,11 @@
       <c r="G650" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="651" spans="2:7">
+      <c r="H650" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="651" spans="2:8">
       <c r="B651" t="s">
         <v>297</v>
       </c>
@@ -28141,8 +29329,11 @@
       <c r="G651" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="652" spans="2:7">
+      <c r="H651" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="652" spans="2:8">
       <c r="B652" t="s">
         <v>297</v>
       </c>
@@ -28158,8 +29349,11 @@
       <c r="G652" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="653" spans="2:7">
+      <c r="H652" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="653" spans="2:8">
       <c r="B653" t="s">
         <v>297</v>
       </c>
@@ -28175,8 +29369,11 @@
       <c r="G653" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="654" spans="2:7">
+      <c r="H653" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="654" spans="2:8">
       <c r="B654" t="s">
         <v>297</v>
       </c>
@@ -28192,8 +29389,11 @@
       <c r="G654" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="655" spans="2:7">
+      <c r="H654" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="655" spans="2:8">
       <c r="B655" t="s">
         <v>297</v>
       </c>
@@ -28209,8 +29409,11 @@
       <c r="G655" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="656" spans="2:7">
+      <c r="H655" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="656" spans="2:8">
       <c r="B656" t="s">
         <v>297</v>
       </c>
@@ -28226,8 +29429,11 @@
       <c r="G656" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="657" spans="2:7">
+      <c r="H656" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="657" spans="2:8">
       <c r="B657" t="s">
         <v>297</v>
       </c>
@@ -28243,8 +29449,11 @@
       <c r="G657" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="658" spans="2:7">
+      <c r="H657" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="658" spans="2:8">
       <c r="B658" t="s">
         <v>297</v>
       </c>
@@ -28260,8 +29469,11 @@
       <c r="G658" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="659" spans="2:7">
+      <c r="H658" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="659" spans="2:8">
       <c r="B659" t="s">
         <v>297</v>
       </c>
@@ -28277,8 +29489,11 @@
       <c r="G659" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="660" spans="2:7">
+      <c r="H659" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="660" spans="2:8">
       <c r="B660" t="s">
         <v>297</v>
       </c>
@@ -28294,8 +29509,11 @@
       <c r="G660" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="661" spans="2:7">
+      <c r="H660" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="661" spans="2:8">
       <c r="B661" t="s">
         <v>297</v>
       </c>
@@ -28311,8 +29529,11 @@
       <c r="G661" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="662" spans="2:7">
+      <c r="H661" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="662" spans="2:8">
       <c r="B662" t="s">
         <v>297</v>
       </c>
@@ -28328,8 +29549,11 @@
       <c r="G662" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="663" spans="2:7">
+      <c r="H662" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="663" spans="2:8">
       <c r="B663" t="s">
         <v>297</v>
       </c>
@@ -28345,8 +29569,11 @@
       <c r="G663" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="664" spans="2:7">
+      <c r="H663" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="664" spans="2:8">
       <c r="B664" t="s">
         <v>297</v>
       </c>
@@ -28362,8 +29589,11 @@
       <c r="G664" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="665" spans="2:7">
+      <c r="H664" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="665" spans="2:8">
       <c r="B665" t="s">
         <v>297</v>
       </c>
@@ -28379,8 +29609,11 @@
       <c r="G665" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="666" spans="2:7">
+      <c r="H665" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="666" spans="2:8">
       <c r="B666" t="s">
         <v>297</v>
       </c>
@@ -28396,8 +29629,11 @@
       <c r="G666" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="667" spans="2:7">
+      <c r="H666" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="667" spans="2:8">
       <c r="B667" t="s">
         <v>297</v>
       </c>
@@ -28413,8 +29649,11 @@
       <c r="G667" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="668" spans="2:7">
+      <c r="H667" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="668" spans="2:8">
       <c r="B668" t="s">
         <v>297</v>
       </c>
@@ -28430,8 +29669,11 @@
       <c r="G668" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="669" spans="2:7">
+      <c r="H668" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="669" spans="2:8">
       <c r="B669" t="s">
         <v>297</v>
       </c>
@@ -28447,8 +29689,11 @@
       <c r="G669" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="670" spans="2:7">
+      <c r="H669" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="670" spans="2:8">
       <c r="B670" t="s">
         <v>297</v>
       </c>
@@ -28464,8 +29709,11 @@
       <c r="G670" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="671" spans="2:7">
+      <c r="H670" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="671" spans="2:8">
       <c r="B671" t="s">
         <v>297</v>
       </c>
@@ -28481,8 +29729,11 @@
       <c r="G671" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="672" spans="2:7">
+      <c r="H671" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="672" spans="2:8">
       <c r="B672" t="s">
         <v>297</v>
       </c>
@@ -28498,8 +29749,11 @@
       <c r="G672" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="673" spans="2:7">
+      <c r="H672" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="673" spans="2:8">
       <c r="B673" t="s">
         <v>297</v>
       </c>
@@ -28515,8 +29769,11 @@
       <c r="G673" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="674" spans="2:7">
+      <c r="H673" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="674" spans="2:8">
       <c r="B674" t="s">
         <v>297</v>
       </c>
@@ -28532,8 +29789,11 @@
       <c r="G674" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="675" spans="2:7">
+      <c r="H674" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="675" spans="2:8">
       <c r="B675" t="s">
         <v>297</v>
       </c>
@@ -28549,8 +29809,11 @@
       <c r="G675" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="676" spans="2:7">
+      <c r="H675" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="676" spans="2:8">
       <c r="B676" t="s">
         <v>297</v>
       </c>
@@ -28565,6 +29828,9 @@
       </c>
       <c r="G676" t="s">
         <v>964</v>
+      </c>
+      <c r="H676" t="s">
+        <v>977</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCE6C87-D8C9-4D93-8ADF-A0AD29051DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{159DAB07-CADD-4F9C-A09C-6972AC2B5D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9129,7 +9129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8191D3E7-570D-4EF7-8FD1-42D7F5B3DFC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85168240-2819-412C-81E8-5895D18F50A4}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16481,7 +16481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EDAB4F-EA3A-461C-A84D-991CDA6B1EB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80139961-872B-4A33-8A9E-1A0226222230}">
   <dimension ref="B9:H676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{159DAB07-CADD-4F9C-A09C-6972AC2B5D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8778596A-AE0B-4451-9C18-88D63EDB7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9129,7 +9129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85168240-2819-412C-81E8-5895D18F50A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AB9B60-92D3-4739-8631-8DE66F4A9F84}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16481,7 +16481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80139961-872B-4A33-8A9E-1A0226222230}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2851D56E-9638-45F1-9DC5-D1A045FF774F}">
   <dimension ref="B9:H676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8778596A-AE0B-4451-9C18-88D63EDB7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14ED6E37-8F7A-4B24-A4C8-FC7647EB1802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9129,7 +9129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AB9B60-92D3-4739-8631-8DE66F4A9F84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D639A65-2009-40C0-AD67-C65139818F53}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16481,7 +16481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2851D56E-9638-45F1-9DC5-D1A045FF774F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1257A1-917F-4789-8579-489D597A82F6}">
   <dimension ref="B9:H676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NZL_grids/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FF8FD8-EECA-4CFC-8FB5-67C4BADDAD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCE063CB-F4A1-4AE8-86B8-0FADD9A6ECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -1241,13 +1241,13 @@
     <t>g64</t>
   </si>
   <si>
-    <t>f97p50</t>
-  </si>
-  <si>
     <t>f96p10</t>
   </si>
   <si>
     <t>f96p90</t>
+  </si>
+  <si>
+    <t>f96p50</t>
   </si>
   <si>
     <t>grid_node</t>
@@ -7052,7 +7052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D921485-FD48-41A0-9773-A9C096BA364A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A602EE4-BFE0-44DA-8D50-447105598C8E}">
   <dimension ref="B9:D676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14404,7 +14404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AFF8E6-5445-42F2-A557-FB4F3086F9C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8236BF-C490-44B1-BFFC-A0957FBF8177}">
   <dimension ref="B9:H676"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28195,7 +28195,7 @@
         <v>337</v>
       </c>
       <c r="U12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="2:24">
@@ -28238,7 +28238,7 @@
         <v>343</v>
       </c>
       <c r="U13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="2:24">
@@ -28281,7 +28281,7 @@
         <v>349</v>
       </c>
       <c r="U14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="2:24">
@@ -29098,11 +29098,11 @@
       </c>
       <c r="C36" t="str">
         <f t="shared" si="5"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="2"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="3"/>
@@ -29110,7 +29110,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -29135,11 +29135,11 @@
       </c>
       <c r="C37" t="str">
         <f t="shared" si="5"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="2"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="3"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N37">
         <v>5</v>
@@ -29172,11 +29172,11 @@
       </c>
       <c r="C38" t="str">
         <f t="shared" si="5"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="2"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="3"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N38">
         <v>5</v>
@@ -29209,11 +29209,11 @@
       </c>
       <c r="C39" t="str">
         <f t="shared" si="5"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="2"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="3"/>
@@ -29221,7 +29221,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -29246,11 +29246,11 @@
       </c>
       <c r="C40" t="str">
         <f t="shared" si="5"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="2"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="3"/>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N40">
         <v>5</v>
